--- a/Project_ETF/ETF_Investment_Portfolio/00403A/ETF_Investment_Portfolio_20260604.xlsx
+++ b/Project_ETF/ETF_Investment_Portfolio/00403A/ETF_Investment_Portfolio_20260604.xlsx
@@ -1305,17 +1305,17 @@
     <row r="53">
       <c r="A53" s="3" t="inlineStr">
         <is>
-          <t>6488</t>
+          <t>8996</t>
         </is>
       </c>
       <c r="B53" s="3" t="inlineStr">
         <is>
-          <t>環球晶</t>
+          <t>高力</t>
         </is>
       </c>
       <c r="C53" s="4" t="inlineStr">
         <is>
-          <t>1,497,000</t>
+          <t>1,169,000</t>
         </is>
       </c>
       <c r="D53" s="4" t="inlineStr">
@@ -1327,17 +1327,17 @@
     <row r="54">
       <c r="A54" s="3" t="inlineStr">
         <is>
-          <t>8996</t>
+          <t>6488</t>
         </is>
       </c>
       <c r="B54" s="3" t="inlineStr">
         <is>
-          <t>高力</t>
+          <t>環球晶</t>
         </is>
       </c>
       <c r="C54" s="4" t="inlineStr">
         <is>
-          <t>1,169,000</t>
+          <t>1,497,000</t>
         </is>
       </c>
       <c r="D54" s="4" t="inlineStr">
@@ -1371,17 +1371,17 @@
     <row r="56">
       <c r="A56" s="3" t="inlineStr">
         <is>
-          <t>8358</t>
+          <t>8210</t>
         </is>
       </c>
       <c r="B56" s="3" t="inlineStr">
         <is>
-          <t>金居</t>
+          <t>勤誠</t>
         </is>
       </c>
       <c r="C56" s="4" t="inlineStr">
         <is>
-          <t>1,710,000</t>
+          <t>680,000</t>
         </is>
       </c>
       <c r="D56" s="4" t="inlineStr">
@@ -1393,17 +1393,17 @@
     <row r="57">
       <c r="A57" s="3" t="inlineStr">
         <is>
-          <t>8210</t>
+          <t>8358</t>
         </is>
       </c>
       <c r="B57" s="3" t="inlineStr">
         <is>
-          <t>勤誠</t>
+          <t>金居</t>
         </is>
       </c>
       <c r="C57" s="4" t="inlineStr">
         <is>
-          <t>680,000</t>
+          <t>1,710,000</t>
         </is>
       </c>
       <c r="D57" s="4" t="inlineStr">
@@ -1437,17 +1437,17 @@
     <row r="59">
       <c r="A59" s="3" t="inlineStr">
         <is>
-          <t>2317</t>
+          <t>RDI_NTD</t>
         </is>
       </c>
       <c r="B59" s="3" t="inlineStr">
         <is>
-          <t>鴻海</t>
+          <t>RECEIVABLES FOR DISPOSAL OF INVESTMENTS</t>
         </is>
       </c>
       <c r="C59" s="4" t="inlineStr">
         <is>
-          <t>3,200,000</t>
+          <t>922,500,587</t>
         </is>
       </c>
       <c r="D59" s="4" t="inlineStr">
@@ -1459,17 +1459,17 @@
     <row r="60">
       <c r="A60" s="3" t="inlineStr">
         <is>
-          <t>RDI_NTD</t>
+          <t>2317</t>
         </is>
       </c>
       <c r="B60" s="3" t="inlineStr">
         <is>
-          <t>RECEIVABLES FOR DISPOSAL OF INVESTMENTS</t>
+          <t>鴻海</t>
         </is>
       </c>
       <c r="C60" s="4" t="inlineStr">
         <is>
-          <t>922,500,587</t>
+          <t>3,200,000</t>
         </is>
       </c>
       <c r="D60" s="4" t="inlineStr">
